--- a/public/downloads/templates/client-ppc-performance-report-template.xlsx
+++ b/public/downloads/templates/client-ppc-performance-report-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Client Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -536,6 +536,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -568,6 +569,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr"/>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
@@ -575,6 +577,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -860,6 +863,8 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
@@ -942,10 +947,19 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Notes: ACOS = Spend / Sales. ROAS = Sales / Spend. Add or remove campaign rows above the TOTAL row — formulas will need to be dragged down to cover new rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Project Amazon PH Academy — Download Center</t>
         </is>
       </c>
     </row>
@@ -961,5 +975,13 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>